--- a/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_시스템구성도.xlsx
+++ b/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_시스템구성도.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="8970"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12165"/>
   </bookViews>
   <sheets>
     <sheet name="20260428_시스템구성도" sheetId="1" r:id="rId1"/>
@@ -112,19 +112,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
+      <xdr:colOff>104775</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>606850</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>487264</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:rowOff>115151</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 2"/>
+        <xdr:cNvPr id="2" name="그림 1"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -137,45 +137,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="47625" y="352425"/>
-          <a:ext cx="7417225" cy="6219825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>430114</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>58001</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7591425" y="371475"/>
+          <a:off x="104775" y="428625"/>
           <a:ext cx="10669489" cy="6096851"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
